--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_los_lagos_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_los_lagos_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:14</t>
+    <t xml:space="preserve">2026-09-29 14:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_los_lagos_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_los_lagos_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:12</t>
+    <t xml:space="preserve">2026-09-29 18:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -521,10 +521,10 @@
         <v>0.78</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>42.25</v>
+        <v>42.26</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>41.47</v>
+        <v>41.48</v>
       </c>
     </row>
     <row r="5">

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_los_lagos_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_los_lagos_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:41</t>
+    <t xml:space="preserve">2026-10-05 04:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
